--- a/results/natural_resources_breakdown/2050/propanol production, biogas, fossil ethylene.xlsx
+++ b/results/natural_resources_breakdown/2050/propanol production, biogas, fossil ethylene.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Propanol production\results\natural_resources_breakdown\2050\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20732CA0-7FBA-4773-9F99-1A34D168C0BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -64,8 +70,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +134,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -174,7 +188,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -206,9 +220,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -240,6 +272,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -415,11 +465,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -433,7 +483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -444,13 +494,13 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.3499234940676084</v>
+        <v>0.34992349406760842</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -461,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.004714903405565394</v>
+        <v>4.7149034055653941E-3</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -478,13 +528,13 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.000448288228307273</v>
+        <v>4.4828822830727302E-4</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -495,13 +545,13 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.006111122461687258</v>
+        <v>6.111122461687258E-3</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -512,13 +562,13 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.2912422752444959</v>
+        <v>0.29124227524449592</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -529,13 +579,13 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.004188258216255834</v>
+        <v>4.1882582162558338E-3</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -546,13 +596,13 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>7.499010223643527E-06</v>
+        <v>7.4990102236435274E-6</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -563,13 +613,13 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>2.24767030776574E-06</v>
+        <v>2.2476703077657399E-6</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -580,13 +630,13 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0.002822244573803901</v>
+        <v>2.8222445738039009E-3</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -597,13 +647,13 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>3.384227388273605E-05</v>
+        <v>3.3842273882736049E-5</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -614,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>0.04035281875950812</v>
+        <v>4.0352818759508122E-2</v>
       </c>
       <c r="E12">
         <v>1</v>
